--- a/lams old findings.xlsx
+++ b/lams old findings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\bdnaspvop1\sntvol\Reporting-S&amp;T-Non_Financial\Reporting\RMC_Common\NZ\CBRM link\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F9FFB1-7ED8-4DB2-A0E3-EB42B1FD2F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59BF56D1-611B-43C6-84E4-45DD8C9B05D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="12" activeTab="14" xr2:uid="{C6D003F1-76EB-47BD-BACD-0241682EF203}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="6" xr2:uid="{C6D003F1-76EB-47BD-BACD-0241682EF203}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3450" uniqueCount="1838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4028" uniqueCount="1874">
   <si>
     <t>Table Name</t>
   </si>
@@ -7312,12 +7312,120 @@
   <si>
     <t>Staff Takeover</t>
   </si>
+  <si>
+    <t>Home ceedit SaadiqOne</t>
+  </si>
+  <si>
+    <t>Home Credit  ref pw-1216221</t>
+  </si>
+  <si>
+    <t>HOME CREDIT REF PWID (1655940)</t>
+  </si>
+  <si>
+    <t>Home Credit (REF:1188879)</t>
+  </si>
+  <si>
+    <t>Saadiq Home Credit REF PWID-1288076</t>
+  </si>
+  <si>
+    <t>Saadiq Home Credit REFFERRAL PWID-1429154</t>
+  </si>
+  <si>
+    <t>HOME FINANCE,PWID-1273296</t>
+  </si>
+  <si>
+    <t>Saadiq Home Credit ,PWID-1273296</t>
+  </si>
+  <si>
+    <t>Home Credit (REF CODE-1149496)</t>
+  </si>
+  <si>
+    <t>Home Loan SD EF CODE PWID-1149528</t>
+  </si>
+  <si>
+    <t>Takeover Reg REFERRAL PWID-1620130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saadiq Takeover Reg  REF PWID-1149496 </t>
+  </si>
+  <si>
+    <t>TPA, PARTIAL</t>
+  </si>
+  <si>
+    <t>HOME</t>
+  </si>
+  <si>
+    <t>Home Credit REFERREL PWID-1288031</t>
+  </si>
+  <si>
+    <t>Home Credit STAFF REF PWID-1469413</t>
+  </si>
+  <si>
+    <t>HOME CREDIT TO</t>
+  </si>
+  <si>
+    <t>Home Credit reffaral rel:1329920)</t>
+  </si>
+  <si>
+    <t>Home Credit  STAFF PWID-1552307</t>
+  </si>
+  <si>
+    <t>Home Credit REF#1407392</t>
+  </si>
+  <si>
+    <t>SIMULTINEOUS</t>
+  </si>
+  <si>
+    <t>Takeover Reg REF PWID-1446314</t>
+  </si>
+  <si>
+    <t>Takeover Reg taff referral pwid-1293588</t>
+  </si>
+  <si>
+    <t>Takeover Reg taff referralpwid-1618075</t>
+  </si>
+  <si>
+    <t>Takeover Reg(1450518)</t>
+  </si>
+  <si>
+    <t>Home Credit  REFERRAL PWID-1162748</t>
+  </si>
+  <si>
+    <t>Home Credit STAFF PWID-1458263</t>
+  </si>
+  <si>
+    <t>Home Credit STAFF REFERRAL PWID-1293588</t>
+  </si>
+  <si>
+    <t>Home Credit staff pwid-1217420</t>
+  </si>
+  <si>
+    <t>Home Credit staff ref pwid-1552307</t>
+  </si>
+  <si>
+    <t>HOME   CREDIT</t>
+  </si>
+  <si>
+    <t>TAKEOVER 2nd</t>
+  </si>
+  <si>
+    <t>CONVERSION</t>
+  </si>
+  <si>
+    <t>SaadiqOne   home credit</t>
+  </si>
+  <si>
+    <t>HOME   CREDIT TO</t>
+  </si>
+  <si>
+    <t>HOME CREDIT referral  pwid-1446314</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7406,8 +7514,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -7447,6 +7561,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7530,7 +7650,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -7626,14 +7746,14 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7652,6 +7772,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8006,13 +8132,13 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="36" t="s">
         <v>107</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -8020,21 +8146,21 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="36"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="37"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="36"/>
       <c r="D4" s="5" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="36" t="s">
         <v>110</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -8042,21 +8168,21 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="36"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="37"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="36"/>
       <c r="D6" s="5" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="36" t="s">
         <v>113</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -8064,21 +8190,21 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="36"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="37"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="36"/>
       <c r="D8" s="5" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="35" t="s">
         <v>77</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -8086,29 +8212,29 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="36"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="36"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="36"/>
-      <c r="B11" s="35"/>
-      <c r="C11" s="36"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="35"/>
       <c r="D11" s="5" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="35" t="s">
         <v>78</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -8116,17 +8242,17 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="36"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="36"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="5" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="36"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="36"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="35"/>
       <c r="D14" s="5" t="s">
         <v>121</v>
       </c>
@@ -8188,13 +8314,13 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="37" t="s">
+      <c r="C19" s="36" t="s">
         <v>130</v>
       </c>
       <c r="D19" s="5" t="s">
@@ -8202,29 +8328,29 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="36"/>
-      <c r="B20" s="35"/>
-      <c r="C20" s="37"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="36"/>
       <c r="D20" s="5" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="36"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="37"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="36"/>
       <c r="D21" s="5" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="36" t="s">
+      <c r="A22" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="B22" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C22" s="35" t="s">
         <v>79</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -8232,37 +8358,37 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="36"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="36"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="35"/>
       <c r="D23" s="5" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="36"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="36"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="35"/>
       <c r="D24" s="5" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="36"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="36"/>
+      <c r="A25" s="35"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="35"/>
       <c r="D25" s="5" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="35" t="s">
+      <c r="B26" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="37" t="s">
+      <c r="C26" s="36" t="s">
         <v>138</v>
       </c>
       <c r="D26" s="5" t="s">
@@ -8270,9 +8396,9 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="36"/>
-      <c r="B27" s="35"/>
-      <c r="C27" s="37"/>
+      <c r="A27" s="35"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="36"/>
       <c r="D27" s="5" t="s">
         <v>140</v>
       </c>
@@ -8292,13 +8418,13 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="36" t="s">
+      <c r="A29" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="35" t="s">
+      <c r="B29" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="36" t="s">
+      <c r="C29" s="35" t="s">
         <v>142</v>
       </c>
       <c r="D29" s="5" t="s">
@@ -8306,29 +8432,29 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="36"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="36"/>
+      <c r="A30" s="35"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="35"/>
       <c r="D30" s="5" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="36"/>
-      <c r="B31" s="35"/>
-      <c r="C31" s="36"/>
+      <c r="A31" s="35"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="35"/>
       <c r="D31" s="5" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="36" t="s">
+      <c r="A32" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="35" t="s">
+      <c r="B32" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="C32" s="35" t="s">
         <v>81</v>
       </c>
       <c r="D32" s="5" t="s">
@@ -8336,21 +8462,21 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="36"/>
-      <c r="B33" s="35"/>
-      <c r="C33" s="36"/>
+      <c r="A33" s="35"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="35"/>
       <c r="D33" s="5" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="36" t="s">
+      <c r="A34" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="35" t="s">
+      <c r="B34" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="36" t="s">
+      <c r="C34" s="35" t="s">
         <v>82</v>
       </c>
       <c r="D34" s="5" t="s">
@@ -8358,29 +8484,29 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="36"/>
-      <c r="B35" s="35"/>
-      <c r="C35" s="36"/>
+      <c r="A35" s="35"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="35"/>
       <c r="D35" s="5" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="36"/>
-      <c r="B36" s="35"/>
-      <c r="C36" s="36"/>
+      <c r="A36" s="35"/>
+      <c r="B36" s="37"/>
+      <c r="C36" s="35"/>
       <c r="D36" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="36" t="s">
+      <c r="A37" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="35" t="s">
+      <c r="B37" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="36" t="s">
+      <c r="C37" s="35" t="s">
         <v>83</v>
       </c>
       <c r="D37" s="5" t="s">
@@ -8388,9 +8514,9 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="36"/>
-      <c r="B38" s="35"/>
-      <c r="C38" s="36"/>
+      <c r="A38" s="35"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="35"/>
       <c r="D38" s="5" t="s">
         <v>152</v>
       </c>
@@ -8410,13 +8536,13 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="36" t="s">
+      <c r="A40" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="35" t="s">
+      <c r="B40" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="36" t="s">
+      <c r="C40" s="35" t="s">
         <v>85</v>
       </c>
       <c r="D40" s="5" t="s">
@@ -8424,29 +8550,29 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="36"/>
-      <c r="B41" s="35"/>
-      <c r="C41" s="36"/>
+      <c r="A41" s="35"/>
+      <c r="B41" s="37"/>
+      <c r="C41" s="35"/>
       <c r="D41" s="5" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="36"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="36"/>
+      <c r="A42" s="35"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="35"/>
       <c r="D42" s="5" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="36" t="s">
+      <c r="A43" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="35" t="s">
+      <c r="B43" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="36" t="s">
+      <c r="C43" s="35" t="s">
         <v>86</v>
       </c>
       <c r="D43" s="5" t="s">
@@ -8454,17 +8580,17 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="36"/>
-      <c r="B44" s="35"/>
-      <c r="C44" s="36"/>
+      <c r="A44" s="35"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="35"/>
       <c r="D44" s="5" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="36"/>
-      <c r="B45" s="35"/>
-      <c r="C45" s="36"/>
+      <c r="A45" s="35"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="35"/>
       <c r="D45" s="5" t="s">
         <v>159</v>
       </c>
@@ -8498,13 +8624,13 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="36" t="s">
+      <c r="A48" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="35" t="s">
+      <c r="B48" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="36" t="s">
+      <c r="C48" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D48" s="5" t="s">
@@ -8512,21 +8638,21 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="36"/>
-      <c r="B49" s="35"/>
-      <c r="C49" s="36"/>
+      <c r="A49" s="35"/>
+      <c r="B49" s="37"/>
+      <c r="C49" s="35"/>
       <c r="D49" s="5" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="36" t="s">
+      <c r="A50" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="35" t="s">
+      <c r="B50" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="C50" s="36" t="s">
+      <c r="C50" s="35" t="s">
         <v>90</v>
       </c>
       <c r="D50" s="5" t="s">
@@ -8534,21 +8660,21 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="36"/>
-      <c r="B51" s="35"/>
-      <c r="C51" s="36"/>
+      <c r="A51" s="35"/>
+      <c r="B51" s="37"/>
+      <c r="C51" s="35"/>
       <c r="D51" s="5" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="36" t="s">
+      <c r="A52" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="35" t="s">
+      <c r="B52" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="C52" s="36" t="s">
+      <c r="C52" s="35" t="s">
         <v>91</v>
       </c>
       <c r="D52" s="5" t="s">
@@ -8556,21 +8682,21 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="36"/>
-      <c r="B53" s="35"/>
-      <c r="C53" s="36"/>
+      <c r="A53" s="35"/>
+      <c r="B53" s="37"/>
+      <c r="C53" s="35"/>
       <c r="D53" s="5" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="36" t="s">
+      <c r="A54" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="35" t="s">
+      <c r="B54" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="C54" s="36" t="s">
+      <c r="C54" s="35" t="s">
         <v>92</v>
       </c>
       <c r="D54" s="5" t="s">
@@ -8578,33 +8704,33 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="36"/>
-      <c r="B55" s="35"/>
-      <c r="C55" s="36"/>
+      <c r="A55" s="35"/>
+      <c r="B55" s="37"/>
+      <c r="C55" s="35"/>
       <c r="D55" s="5" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="36"/>
-      <c r="B56" s="35"/>
-      <c r="C56" s="36"/>
+      <c r="A56" s="35"/>
+      <c r="B56" s="37"/>
+      <c r="C56" s="35"/>
       <c r="D56" s="5" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="36"/>
-      <c r="B57" s="35"/>
-      <c r="C57" s="36"/>
+      <c r="A57" s="35"/>
+      <c r="B57" s="37"/>
+      <c r="C57" s="35"/>
       <c r="D57" s="5" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="36"/>
-      <c r="B58" s="35"/>
-      <c r="C58" s="36"/>
+      <c r="A58" s="35"/>
+      <c r="B58" s="37"/>
+      <c r="C58" s="35"/>
       <c r="D58" s="5" t="s">
         <v>172</v>
       </c>
@@ -8666,13 +8792,13 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="36" t="s">
+      <c r="A63" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="35" t="s">
+      <c r="B63" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="C63" s="36" t="s">
+      <c r="C63" s="35" t="s">
         <v>98</v>
       </c>
       <c r="D63" s="5" t="s">
@@ -8680,9 +8806,9 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="36"/>
-      <c r="B64" s="35"/>
-      <c r="C64" s="36"/>
+      <c r="A64" s="35"/>
+      <c r="B64" s="37"/>
+      <c r="C64" s="35"/>
       <c r="D64" s="5" t="s">
         <v>177</v>
       </c>
@@ -8759,51 +8885,6 @@
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="A43:A45"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B40:B42"/>
     <mergeCell ref="B63:B64"/>
     <mergeCell ref="A63:A64"/>
     <mergeCell ref="C63:C64"/>
@@ -8816,6 +8897,51 @@
     <mergeCell ref="B50:B51"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="B54:B58"/>
+    <mergeCell ref="A40:A42"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B3:B4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -13184,13 +13310,13 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="36" t="s">
         <v>107</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -13198,21 +13324,21 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="36"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="37"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="36"/>
       <c r="D4" s="5" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="36" t="s">
         <v>110</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -13220,21 +13346,21 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="36"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="37"/>
+      <c r="A6" s="35"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="36"/>
       <c r="D6" s="5" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="B7" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="36" t="s">
         <v>113</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -13242,21 +13368,21 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="36"/>
-      <c r="B8" s="35"/>
-      <c r="C8" s="37"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="36"/>
       <c r="D8" s="5" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="B9" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="35" t="s">
         <v>77</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -13264,29 +13390,29 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="36"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="36"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="35"/>
       <c r="D10" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="36"/>
-      <c r="B11" s="35"/>
-      <c r="C11" s="36"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="35"/>
       <c r="D11" s="5" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="35" t="s">
         <v>78</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -13294,17 +13420,17 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="36"/>
-      <c r="B13" s="35"/>
-      <c r="C13" s="36"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="35"/>
       <c r="D13" s="5" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="36"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="36"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="35"/>
       <c r="D14" s="5" t="s">
         <v>121</v>
       </c>
@@ -13362,13 +13488,13 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="37" t="s">
+      <c r="C19" s="36" t="s">
         <v>130</v>
       </c>
       <c r="D19" s="5" t="s">
@@ -13376,29 +13502,29 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="36"/>
-      <c r="B20" s="35"/>
-      <c r="C20" s="37"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="36"/>
       <c r="D20" s="5" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="36"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="37"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="36"/>
       <c r="D21" s="5" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="36" t="s">
+      <c r="A22" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="B22" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C22" s="35" t="s">
         <v>79</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -13406,37 +13532,37 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="36"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="36"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="35"/>
       <c r="D23" s="5" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="36"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="36"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="35"/>
       <c r="D24" s="5" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="36"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="36"/>
+      <c r="A25" s="35"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="35"/>
       <c r="D25" s="5" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="35" t="s">
+      <c r="B26" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="37" t="s">
+      <c r="C26" s="36" t="s">
         <v>138</v>
       </c>
       <c r="D26" s="5" t="s">
@@ -13444,9 +13570,9 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="36"/>
-      <c r="B27" s="35"/>
-      <c r="C27" s="37"/>
+      <c r="A27" s="35"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="36"/>
       <c r="D27" s="5" t="s">
         <v>140</v>
       </c>
@@ -13466,13 +13592,13 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="36" t="s">
+      <c r="A29" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="35" t="s">
+      <c r="B29" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="36" t="s">
+      <c r="C29" s="35" t="s">
         <v>142</v>
       </c>
       <c r="D29" s="5" t="s">
@@ -13480,29 +13606,29 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="36"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="36"/>
+      <c r="A30" s="35"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="35"/>
       <c r="D30" s="5" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="36"/>
-      <c r="B31" s="35"/>
-      <c r="C31" s="36"/>
+      <c r="A31" s="35"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="35"/>
       <c r="D31" s="5" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="36" t="s">
+      <c r="A32" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="35" t="s">
+      <c r="B32" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="C32" s="35" t="s">
         <v>81</v>
       </c>
       <c r="D32" s="5" t="s">
@@ -13510,21 +13636,21 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="36"/>
-      <c r="B33" s="35"/>
-      <c r="C33" s="36"/>
+      <c r="A33" s="35"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="35"/>
       <c r="D33" s="5" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="36" t="s">
+      <c r="A34" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="35" t="s">
+      <c r="B34" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="36" t="s">
+      <c r="C34" s="35" t="s">
         <v>82</v>
       </c>
       <c r="D34" s="5" t="s">
@@ -13532,29 +13658,29 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="36"/>
-      <c r="B35" s="35"/>
-      <c r="C35" s="36"/>
+      <c r="A35" s="35"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="35"/>
       <c r="D35" s="5" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="36"/>
-      <c r="B36" s="35"/>
-      <c r="C36" s="36"/>
+      <c r="A36" s="35"/>
+      <c r="B36" s="37"/>
+      <c r="C36" s="35"/>
       <c r="D36" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="36" t="s">
+      <c r="A37" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="35" t="s">
+      <c r="B37" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="36" t="s">
+      <c r="C37" s="35" t="s">
         <v>83</v>
       </c>
       <c r="D37" s="5" t="s">
@@ -13562,9 +13688,9 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="36"/>
-      <c r="B38" s="35"/>
-      <c r="C38" s="36"/>
+      <c r="A38" s="35"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="35"/>
       <c r="D38" s="5" t="s">
         <v>152</v>
       </c>
@@ -13584,13 +13710,13 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="36" t="s">
+      <c r="A40" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="35" t="s">
+      <c r="B40" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="36" t="s">
+      <c r="C40" s="35" t="s">
         <v>85</v>
       </c>
       <c r="D40" s="5" t="s">
@@ -13598,29 +13724,29 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="36"/>
-      <c r="B41" s="35"/>
-      <c r="C41" s="36"/>
+      <c r="A41" s="35"/>
+      <c r="B41" s="37"/>
+      <c r="C41" s="35"/>
       <c r="D41" s="5" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="36"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="36"/>
+      <c r="A42" s="35"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="35"/>
       <c r="D42" s="5" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="36" t="s">
+      <c r="A43" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="35" t="s">
+      <c r="B43" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="36" t="s">
+      <c r="C43" s="35" t="s">
         <v>86</v>
       </c>
       <c r="D43" s="5" t="s">
@@ -13628,17 +13754,17 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="36"/>
-      <c r="B44" s="35"/>
-      <c r="C44" s="36"/>
+      <c r="A44" s="35"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="35"/>
       <c r="D44" s="5" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="36"/>
-      <c r="B45" s="35"/>
-      <c r="C45" s="36"/>
+      <c r="A45" s="35"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="35"/>
       <c r="D45" s="5" t="s">
         <v>159</v>
       </c>
@@ -13672,13 +13798,13 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="36" t="s">
+      <c r="A48" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="35" t="s">
+      <c r="B48" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="36" t="s">
+      <c r="C48" s="35" t="s">
         <v>89</v>
       </c>
       <c r="D48" s="5" t="s">
@@ -13686,21 +13812,21 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="36"/>
-      <c r="B49" s="35"/>
-      <c r="C49" s="36"/>
+      <c r="A49" s="35"/>
+      <c r="B49" s="37"/>
+      <c r="C49" s="35"/>
       <c r="D49" s="5" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="36" t="s">
+      <c r="A50" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="35" t="s">
+      <c r="B50" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="C50" s="36" t="s">
+      <c r="C50" s="35" t="s">
         <v>90</v>
       </c>
       <c r="D50" s="5" t="s">
@@ -13708,21 +13834,21 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="36"/>
-      <c r="B51" s="35"/>
-      <c r="C51" s="36"/>
+      <c r="A51" s="35"/>
+      <c r="B51" s="37"/>
+      <c r="C51" s="35"/>
       <c r="D51" s="5" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="36" t="s">
+      <c r="A52" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="35" t="s">
+      <c r="B52" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="C52" s="36" t="s">
+      <c r="C52" s="35" t="s">
         <v>91</v>
       </c>
       <c r="D52" s="5" t="s">
@@ -13730,19 +13856,19 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="36"/>
-      <c r="B53" s="35"/>
-      <c r="C53" s="36"/>
+      <c r="A53" s="35"/>
+      <c r="B53" s="37"/>
+      <c r="C53" s="35"/>
       <c r="D53" s="5" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="36" t="s">
+      <c r="A54" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="35"/>
-      <c r="C54" s="36" t="s">
+      <c r="B54" s="37"/>
+      <c r="C54" s="35" t="s">
         <v>92</v>
       </c>
       <c r="D54" s="5" t="s">
@@ -13750,33 +13876,33 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="36"/>
-      <c r="B55" s="35"/>
-      <c r="C55" s="36"/>
+      <c r="A55" s="35"/>
+      <c r="B55" s="37"/>
+      <c r="C55" s="35"/>
       <c r="D55" s="5" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="36"/>
-      <c r="B56" s="35"/>
-      <c r="C56" s="36"/>
+      <c r="A56" s="35"/>
+      <c r="B56" s="37"/>
+      <c r="C56" s="35"/>
       <c r="D56" s="5" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="36"/>
-      <c r="B57" s="35"/>
-      <c r="C57" s="36"/>
+      <c r="A57" s="35"/>
+      <c r="B57" s="37"/>
+      <c r="C57" s="35"/>
       <c r="D57" s="5" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="36"/>
-      <c r="B58" s="35"/>
-      <c r="C58" s="36"/>
+      <c r="A58" s="35"/>
+      <c r="B58" s="37"/>
+      <c r="C58" s="35"/>
       <c r="D58" s="5" t="s">
         <v>172</v>
       </c>
@@ -13830,11 +13956,11 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="36" t="s">
+      <c r="A63" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="B63" s="35"/>
-      <c r="C63" s="36" t="s">
+      <c r="B63" s="37"/>
+      <c r="C63" s="35" t="s">
         <v>98</v>
       </c>
       <c r="D63" s="5" t="s">
@@ -13842,9 +13968,9 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="36"/>
-      <c r="B64" s="35"/>
-      <c r="C64" s="36"/>
+      <c r="A64" s="35"/>
+      <c r="B64" s="37"/>
+      <c r="C64" s="35"/>
       <c r="D64" s="5" t="s">
         <v>177</v>
       </c>
@@ -13893,6 +14019,54 @@
     </row>
   </sheetData>
   <mergeCells count="57">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="A40:A42"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
     <mergeCell ref="A63:A64"/>
     <mergeCell ref="B63:B64"/>
     <mergeCell ref="C63:C64"/>
@@ -13902,54 +14076,6 @@
     <mergeCell ref="A54:A58"/>
     <mergeCell ref="B54:B58"/>
     <mergeCell ref="C54:C58"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="A40:A42"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="A43:A45"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -20482,24 +20608,18 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E77AFD7-D029-463A-B4BE-501965644DB3}">
-  <dimension ref="B2:J326"/>
+  <dimension ref="A2:J326"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.7265625" customWidth="1"/>
     <col min="2" max="2" width="23.7265625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="3" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C3" t="s">
-        <v>441</v>
-      </c>
+    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F3">
         <v>6865736</v>
       </c>
@@ -20508,63 +20628,72 @@
       </c>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C4" t="s">
-        <v>441</v>
+    <row r="4" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="44" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>1823</v>
       </c>
       <c r="F4" t="s">
         <v>1509</v>
       </c>
-      <c r="G4" t="s">
-        <v>441</v>
-      </c>
       <c r="I4" s="31" t="s">
         <v>1694</v>
       </c>
       <c r="J4" s="32"/>
     </row>
-    <row r="5" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="44" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F5" t="s">
         <v>1510</v>
       </c>
-      <c r="G5" t="s">
-        <v>441</v>
-      </c>
       <c r="I5" s="31" t="s">
         <v>1822</v>
       </c>
       <c r="J5" s="32"/>
     </row>
-    <row r="6" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="44" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>1829</v>
+      </c>
       <c r="F6" t="s">
         <v>1511</v>
       </c>
-      <c r="G6" t="s">
-        <v>441</v>
-      </c>
       <c r="I6" s="31" t="s">
         <v>1823</v>
       </c>
       <c r="J6" s="32"/>
     </row>
-    <row r="7" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C7" t="s">
-        <v>443</v>
+    <row r="7" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="44" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>1823</v>
       </c>
       <c r="F7" t="s">
         <v>1506</v>
       </c>
-      <c r="G7" t="s">
-        <v>441</v>
-      </c>
       <c r="I7" s="31" t="s">
         <v>1824</v>
       </c>
       <c r="J7" s="32"/>
     </row>
-    <row r="8" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C8" t="s">
-        <v>443</v>
+    <row r="8" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="44" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B8" s="45" t="s">
+        <v>1830</v>
       </c>
       <c r="F8" t="s">
         <v>1512</v>
@@ -20574,7 +20703,13 @@
       </c>
       <c r="J8" s="32"/>
     </row>
-    <row r="9" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="44" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F9" t="s">
         <v>1513</v>
       </c>
@@ -20583,9 +20718,12 @@
       </c>
       <c r="J9" s="32"/>
     </row>
-    <row r="10" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C10" t="s">
-        <v>438</v>
+    <row r="10" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="44" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>1839</v>
       </c>
       <c r="F10" t="s">
         <v>1514</v>
@@ -20595,70 +20733,74 @@
       </c>
       <c r="J10" s="32"/>
     </row>
-    <row r="11" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C11" t="s">
-        <v>439</v>
+    <row r="11" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="44" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>1823</v>
       </c>
       <c r="F11" t="s">
         <v>1515</v>
       </c>
-      <c r="G11" t="s">
-        <v>1819</v>
-      </c>
       <c r="I11" s="31" t="s">
         <v>1819</v>
       </c>
       <c r="J11" s="32"/>
     </row>
-    <row r="12" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C12" t="s">
-        <v>440</v>
+    <row r="12" spans="1:10" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="44" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>1840</v>
       </c>
       <c r="F12" t="s">
         <v>1516</v>
       </c>
-      <c r="G12" t="s">
-        <v>1694</v>
-      </c>
       <c r="I12" s="31" t="s">
         <v>1828</v>
       </c>
       <c r="J12" s="32"/>
     </row>
-    <row r="13" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C13" t="s">
-        <v>441</v>
+    <row r="13" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="44" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>1841</v>
       </c>
       <c r="F13" t="s">
         <v>1517</v>
       </c>
-      <c r="G13" t="s">
-        <v>1820</v>
-      </c>
       <c r="I13" s="31" t="s">
         <v>1829</v>
       </c>
       <c r="J13" s="32"/>
     </row>
-    <row r="14" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C14" t="s">
-        <v>442</v>
+    <row r="14" spans="1:10" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="44" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>1518</v>
       </c>
       <c r="F14" t="s">
         <v>1518</v>
       </c>
-      <c r="G14" s="28" t="s">
-        <v>1565</v>
-      </c>
+      <c r="G14" s="28"/>
       <c r="H14" s="28"/>
       <c r="I14" s="31" t="s">
         <v>1820</v>
       </c>
       <c r="J14" s="32"/>
     </row>
-    <row r="15" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C15" t="s">
-        <v>443</v>
+    <row r="15" spans="1:10" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="44" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B15" s="44" t="s">
+        <v>1519</v>
       </c>
       <c r="F15" t="s">
         <v>1519</v>
@@ -20670,9 +20812,12 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="16" spans="3:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C16" t="s">
-        <v>444</v>
+    <row r="16" spans="1:10" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="44" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>1823</v>
       </c>
       <c r="F16" t="s">
         <v>1520</v>
@@ -20684,9 +20829,12 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="17" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C17" t="s">
-        <v>445</v>
+    <row r="17" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="44" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>1824</v>
       </c>
       <c r="F17" t="s">
         <v>1521</v>
@@ -20698,9 +20846,12 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="18" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C18" t="s">
-        <v>446</v>
+    <row r="18" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="44" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>1824</v>
       </c>
       <c r="F18" t="s">
         <v>1522</v>
@@ -20712,9 +20863,12 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="19" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C19" t="s">
-        <v>447</v>
+    <row r="19" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="44" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>1826</v>
       </c>
       <c r="F19" t="s">
         <v>1523</v>
@@ -20724,9 +20878,12 @@
       </c>
       <c r="J19" s="32"/>
     </row>
-    <row r="20" spans="2:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" t="s">
-        <v>448</v>
+    <row r="20" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="44" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>1829</v>
       </c>
       <c r="F20" t="s">
         <v>1524</v>
@@ -20736,9 +20893,12 @@
       </c>
       <c r="J20" s="32"/>
     </row>
-    <row r="21" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B21" t="s">
-        <v>449</v>
+    <row r="21" spans="1:10" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="44" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>1842</v>
       </c>
       <c r="F21" t="s">
         <v>1525</v>
@@ -20750,1575 +20910,3297 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B22" t="s">
-        <v>450</v>
+    <row r="22" spans="1:10" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="44" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>1843</v>
       </c>
       <c r="F22" t="s">
         <v>1526</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B23" t="s">
-        <v>451</v>
+    <row r="23" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="44" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>1827</v>
       </c>
       <c r="F23" t="s">
         <v>1527</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B24" t="s">
-        <v>452</v>
+    <row r="24" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="44" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>1830</v>
       </c>
       <c r="F24" t="s">
         <v>1528</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B25" t="s">
-        <v>453</v>
+    <row r="25" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="44" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>1845</v>
       </c>
       <c r="F25" t="s">
         <v>1529</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B26" t="s">
-        <v>454</v>
+    <row r="26" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="44" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>1823</v>
       </c>
       <c r="F26" t="s">
         <v>1530</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B27" t="s">
-        <v>441</v>
+    <row r="27" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="44" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>1830</v>
       </c>
       <c r="F27" t="s">
         <v>1531</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B28" t="s">
-        <v>442</v>
+    <row r="28" spans="1:10" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="44" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>1846</v>
       </c>
       <c r="F28" t="s">
         <v>1532</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B29" t="s">
-        <v>443</v>
+    <row r="29" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="44" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>1823</v>
       </c>
       <c r="F29" t="s">
         <v>1533</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B30" t="s">
-        <v>444</v>
+    <row r="30" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="44" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B30" s="31" t="s">
+        <v>1823</v>
       </c>
       <c r="F30" t="s">
         <v>1534</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B31" t="s">
-        <v>455</v>
+    <row r="31" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="44" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B31" s="31" t="s">
+        <v>1823</v>
       </c>
       <c r="F31" t="s">
         <v>1535</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B32" t="s">
-        <v>456</v>
+    <row r="32" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="44" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B32" s="31" t="s">
+        <v>1823</v>
       </c>
       <c r="F32" t="s">
         <v>1536</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B33" t="s">
-        <v>457</v>
+    <row r="33" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="44" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B33" s="31" t="s">
+        <v>1694</v>
       </c>
       <c r="F33" t="s">
         <v>1537</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B34" t="s">
-        <v>448</v>
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+      <c r="A34" s="44" t="s">
+        <v>1538</v>
       </c>
       <c r="F34" t="s">
         <v>1538</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B35" t="s">
-        <v>449</v>
+    <row r="35" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="44" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B35" s="31" t="s">
+        <v>1847</v>
       </c>
       <c r="F35" t="s">
         <v>1539</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" t="s">
-        <v>450</v>
+    <row r="36" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="44" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B36" s="31" t="s">
+        <v>1694</v>
       </c>
       <c r="F36" t="s">
         <v>1540</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B37" t="s">
-        <v>451</v>
+    <row r="37" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="44" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B37" s="33" t="s">
+        <v>1834</v>
       </c>
       <c r="F37" t="s">
         <v>1541</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="44" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F38" t="s">
         <v>1542</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="44" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F39" t="s">
         <v>1543</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="44" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B40" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F40" t="s">
         <v>1544</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="44" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B41" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F41" t="s">
         <v>1545</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="44" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B42" s="31" t="s">
+        <v>1848</v>
+      </c>
       <c r="F42" t="s">
         <v>1546</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="44" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B43" s="31" t="s">
+        <v>1849</v>
+      </c>
       <c r="F43" t="s">
         <v>1547</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="44" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F44" t="s">
         <v>1548</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="44" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B45" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F45" t="s">
         <v>1549</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="44" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>1824</v>
+      </c>
       <c r="F46" t="s">
         <v>1550</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="44" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B47" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F47" t="s">
         <v>1551</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="44" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B48" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F48" t="s">
         <v>1552</v>
       </c>
     </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="44" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B49" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F49" t="s">
         <v>1553</v>
       </c>
     </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="44" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B50" s="31" t="s">
+        <v>1825</v>
+      </c>
       <c r="F50" t="s">
         <v>1554</v>
       </c>
     </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="44" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B51" s="31" t="s">
+        <v>1827</v>
+      </c>
       <c r="F51" t="s">
         <v>1555</v>
       </c>
     </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+      <c r="A52" s="44">
+        <v>16250000</v>
+      </c>
       <c r="F52">
         <v>16250000</v>
       </c>
     </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="44">
+        <v>44</v>
+      </c>
       <c r="F53">
         <v>44</v>
       </c>
     </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="44" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B54" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F54" t="s">
         <v>1556</v>
       </c>
     </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="44" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B55" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F55" t="s">
         <v>1557</v>
       </c>
     </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="44" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B56" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F56" t="s">
         <v>1558</v>
       </c>
     </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="44" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B57" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F57" t="s">
         <v>1559</v>
       </c>
     </row>
-    <row r="58" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="44" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B58" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F58" t="s">
         <v>1560</v>
       </c>
     </row>
-    <row r="59" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="44" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B59" s="31" t="s">
+        <v>1852</v>
+      </c>
       <c r="F59" t="s">
         <v>1561</v>
       </c>
     </row>
-    <row r="60" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="44" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B60" s="31" t="s">
+        <v>1853</v>
+      </c>
       <c r="F60" t="s">
         <v>1562</v>
       </c>
     </row>
-    <row r="61" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="44" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B61" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F61" t="s">
         <v>1563</v>
       </c>
     </row>
-    <row r="62" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="44" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B62" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F62" t="s">
         <v>1564</v>
       </c>
     </row>
-    <row r="63" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="44" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B63" s="31" t="s">
+        <v>1824</v>
+      </c>
       <c r="F63" t="s">
         <v>1565</v>
       </c>
     </row>
-    <row r="64" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="44" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B64" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F64" t="s">
         <v>1566</v>
       </c>
     </row>
-    <row r="65" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="44" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B65" s="31" t="s">
+        <v>1855</v>
+      </c>
       <c r="F65" t="s">
         <v>1567</v>
       </c>
     </row>
-    <row r="66" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="44" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B66" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F66" t="s">
         <v>1568</v>
       </c>
     </row>
-    <row r="67" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="44" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B67" s="31" t="s">
+        <v>1856</v>
+      </c>
       <c r="F67" t="s">
         <v>1569</v>
       </c>
     </row>
-    <row r="68" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="44" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B68" s="31" t="s">
+        <v>1857</v>
+      </c>
       <c r="F68" t="s">
         <v>1570</v>
       </c>
     </row>
-    <row r="69" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="44" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B69" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F69" t="s">
         <v>1571</v>
       </c>
     </row>
-    <row r="70" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="44" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B70" s="31" t="s">
+        <v>1827</v>
+      </c>
       <c r="F70" t="s">
         <v>1572</v>
       </c>
     </row>
-    <row r="71" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="44" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B71" s="31" t="s">
+        <v>1827</v>
+      </c>
       <c r="F71" t="s">
         <v>1573</v>
       </c>
     </row>
-    <row r="72" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="44" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B72" s="31" t="s">
+        <v>1819</v>
+      </c>
       <c r="F72" t="s">
         <v>1574</v>
       </c>
     </row>
-    <row r="73" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="44" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B73" s="31" t="s">
+        <v>1819</v>
+      </c>
       <c r="F73" t="s">
         <v>1575</v>
       </c>
     </row>
-    <row r="74" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="44" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B74" s="31" t="s">
+        <v>1822</v>
+      </c>
       <c r="F74" t="s">
         <v>1576</v>
       </c>
     </row>
-    <row r="75" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="44" t="s">
+        <v>1577</v>
+      </c>
       <c r="F75" t="s">
         <v>1577</v>
       </c>
     </row>
-    <row r="76" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="44" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B76" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F76" t="s">
         <v>1578</v>
       </c>
     </row>
-    <row r="77" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="44" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B77" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F77" t="s">
         <v>1579</v>
       </c>
     </row>
-    <row r="78" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="44" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B78" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F78" t="s">
         <v>1580</v>
       </c>
     </row>
-    <row r="79" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="44" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B79" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F79" t="s">
         <v>1581</v>
       </c>
     </row>
-    <row r="80" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="44" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B80" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F80" t="s">
         <v>1582</v>
       </c>
     </row>
-    <row r="81" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+      <c r="A81" s="44" t="s">
+        <v>1583</v>
+      </c>
       <c r="F81" t="s">
         <v>1583</v>
       </c>
     </row>
-    <row r="82" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+      <c r="A82" s="44" t="s">
+        <v>1584</v>
+      </c>
       <c r="F82" t="s">
         <v>1584</v>
       </c>
     </row>
-    <row r="83" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="44" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B83" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F83" t="s">
         <v>1585</v>
       </c>
     </row>
-    <row r="84" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="44" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B84" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F84" t="s">
         <v>1586</v>
       </c>
     </row>
-    <row r="85" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="44" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B85" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F85" t="s">
         <v>1587</v>
       </c>
     </row>
-    <row r="86" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="44" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B86" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F86" t="s">
         <v>1588</v>
       </c>
     </row>
-    <row r="87" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="44" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B87" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F87" t="s">
         <v>1589</v>
       </c>
     </row>
-    <row r="88" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A88" s="44" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B88" s="31" t="s">
+        <v>1829</v>
+      </c>
       <c r="F88" t="s">
         <v>1590</v>
       </c>
     </row>
-    <row r="89" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A89" s="44" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B89" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F89" t="s">
         <v>1591</v>
       </c>
     </row>
-    <row r="90" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A90" s="44" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B90" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F90" t="s">
         <v>1592</v>
       </c>
     </row>
-    <row r="91" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="44" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B91" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F91" t="s">
         <v>1593</v>
       </c>
     </row>
-    <row r="92" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A92" s="44" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B92" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F92" t="s">
         <v>1594</v>
       </c>
     </row>
-    <row r="93" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A93" s="44" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B93" s="33" t="s">
+        <v>1832</v>
+      </c>
       <c r="F93" t="s">
         <v>1595</v>
       </c>
     </row>
-    <row r="94" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A94" s="44" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B94" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F94" t="s">
         <v>1596</v>
       </c>
     </row>
-    <row r="95" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A95" s="44" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B95" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F95" t="s">
         <v>1597</v>
       </c>
     </row>
-    <row r="96" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A96" s="44" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B96" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F96" t="s">
         <v>1598</v>
       </c>
     </row>
-    <row r="97" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A97" s="44" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B97" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F97" t="s">
         <v>1599</v>
       </c>
     </row>
-    <row r="98" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A98" s="44" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B98" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F98" t="s">
         <v>1600</v>
       </c>
     </row>
-    <row r="99" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A99" s="44" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B99" s="31" t="s">
+        <v>1859</v>
+      </c>
       <c r="F99" t="s">
         <v>1601</v>
       </c>
     </row>
-    <row r="100" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A100" s="44" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B100" s="31" t="s">
+        <v>1860</v>
+      </c>
       <c r="F100" t="s">
         <v>1602</v>
       </c>
     </row>
-    <row r="101" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A101" s="44" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B101" s="34" t="s">
+        <v>1837</v>
+      </c>
       <c r="F101" t="s">
         <v>1603</v>
       </c>
     </row>
-    <row r="102" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A102" s="44" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B102" s="31" t="s">
+        <v>1861</v>
+      </c>
       <c r="F102" t="s">
         <v>1604</v>
       </c>
     </row>
-    <row r="103" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A103" s="44" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B103" s="31" t="s">
+        <v>1825</v>
+      </c>
       <c r="F103" t="s">
         <v>1508</v>
       </c>
     </row>
-    <row r="104" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A104" s="44" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B104" s="31" t="s">
+        <v>1862</v>
+      </c>
       <c r="F104" t="s">
         <v>1605</v>
       </c>
     </row>
-    <row r="105" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A105" s="44" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B105" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F105" t="s">
         <v>1606</v>
       </c>
     </row>
-    <row r="106" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A106" s="44" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B106" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F106" t="s">
         <v>1607</v>
       </c>
     </row>
-    <row r="107" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A107" s="44" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B107" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F107" t="s">
         <v>1608</v>
       </c>
     </row>
-    <row r="108" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A108" s="44" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B108" s="31" t="s">
+        <v>1825</v>
+      </c>
       <c r="F108" t="s">
         <v>1609</v>
       </c>
     </row>
-    <row r="109" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A109" s="44" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B109" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F109" t="s">
         <v>1610</v>
       </c>
     </row>
-    <row r="110" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A110" s="29" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B110" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F110" t="s">
         <v>1611</v>
       </c>
     </row>
-    <row r="111" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A111" s="44" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B111" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F111" t="s">
         <v>1612</v>
       </c>
     </row>
-    <row r="112" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A112" s="44" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B112" s="33" t="s">
+        <v>1830</v>
+      </c>
       <c r="F112" t="s">
         <v>1613</v>
       </c>
     </row>
-    <row r="113" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A113" s="44" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B113" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F113" t="s">
         <v>1328</v>
       </c>
     </row>
-    <row r="114" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A114" s="44" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B114" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F114" t="s">
         <v>1614</v>
       </c>
     </row>
-    <row r="115" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A115" s="44" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B115" s="33" t="s">
+        <v>1830</v>
+      </c>
       <c r="F115" t="s">
         <v>1615</v>
       </c>
     </row>
-    <row r="116" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A116" s="44" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B116" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F116" t="s">
         <v>1616</v>
       </c>
     </row>
-    <row r="117" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A117" s="44" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B117" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F117" t="s">
         <v>1617</v>
       </c>
     </row>
-    <row r="118" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A118" s="44" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B118" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F118" t="s">
         <v>1618</v>
       </c>
     </row>
-    <row r="119" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A119" s="44" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B119" s="31" t="s">
+        <v>1863</v>
+      </c>
       <c r="F119" t="s">
         <v>1619</v>
       </c>
     </row>
-    <row r="120" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A120" s="44" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B120" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F120" t="s">
         <v>1620</v>
       </c>
     </row>
-    <row r="121" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A121" s="44" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B121" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F121" t="s">
         <v>1621</v>
       </c>
     </row>
-    <row r="122" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A122" s="44" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B122" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F122" t="s">
         <v>1622</v>
       </c>
     </row>
-    <row r="123" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A123" s="44" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B123" s="31" t="s">
+        <v>1864</v>
+      </c>
       <c r="F123" t="s">
         <v>1623</v>
       </c>
     </row>
-    <row r="124" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A124" s="44" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B124" s="31" t="s">
+        <v>1865</v>
+      </c>
       <c r="F124" t="s">
         <v>1624</v>
       </c>
     </row>
-    <row r="125" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A125" s="44" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B125" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F125" t="s">
         <v>1625</v>
       </c>
     </row>
-    <row r="126" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A126" s="44" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B126" s="31" t="s">
+        <v>1866</v>
+      </c>
       <c r="F126" t="s">
         <v>1626</v>
       </c>
     </row>
-    <row r="127" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A127" s="44" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B127" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F127" t="s">
         <v>1627</v>
       </c>
     </row>
-    <row r="128" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A128" s="44" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B128" s="31" t="s">
+        <v>1867</v>
+      </c>
       <c r="F128" t="s">
         <v>1628</v>
       </c>
     </row>
-    <row r="129" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A129" s="44" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B129" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F129" t="s">
         <v>1629</v>
       </c>
     </row>
-    <row r="130" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A130" s="44" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B130" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F130" t="s">
         <v>1630</v>
       </c>
     </row>
-    <row r="131" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A131" s="44" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B131" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F131" t="s">
         <v>1631</v>
       </c>
     </row>
-    <row r="132" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A132" s="44" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B132" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F132" t="s">
         <v>1632</v>
       </c>
     </row>
-    <row r="133" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A133" s="44" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B133" s="31" t="s">
+        <v>1819</v>
+      </c>
       <c r="F133" t="s">
         <v>1633</v>
       </c>
     </row>
-    <row r="134" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A134" s="44" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B134" s="31" t="s">
+        <v>1836</v>
+      </c>
       <c r="F134" t="s">
         <v>1634</v>
       </c>
     </row>
-    <row r="135" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A135" s="44" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B135" s="31" t="s">
+        <v>1819</v>
+      </c>
       <c r="F135" t="s">
         <v>1635</v>
       </c>
     </row>
-    <row r="136" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A136" s="44" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B136" s="31" t="s">
+        <v>1836</v>
+      </c>
       <c r="F136" t="s">
         <v>1636</v>
       </c>
     </row>
-    <row r="137" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A137" s="44" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B137" s="31" t="s">
+        <v>1819</v>
+      </c>
       <c r="F137" t="s">
         <v>1637</v>
       </c>
     </row>
-    <row r="138" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A138" s="44" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B138" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F138" t="s">
         <v>1638</v>
       </c>
     </row>
-    <row r="139" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A139" s="44" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B139" s="33" t="s">
+        <v>1830</v>
+      </c>
       <c r="F139" t="s">
         <v>1639</v>
       </c>
     </row>
-    <row r="140" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A140" s="44" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B140" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F140" t="s">
         <v>1640</v>
       </c>
     </row>
-    <row r="141" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A141" s="44" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B141" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F141" t="s">
         <v>1641</v>
       </c>
     </row>
-    <row r="142" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A142" s="44" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B142" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F142" t="s">
         <v>1642</v>
       </c>
     </row>
-    <row r="143" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A143" s="44" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B143" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F143" t="s">
         <v>1643</v>
       </c>
     </row>
-    <row r="144" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A144" s="44" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B144" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F144" t="s">
         <v>1644</v>
       </c>
     </row>
-    <row r="145" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A145" s="44" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B145" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F145" t="s">
         <v>1645</v>
       </c>
     </row>
-    <row r="146" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A146" s="44" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B146" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F146" t="s">
         <v>1646</v>
       </c>
     </row>
-    <row r="147" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A147" s="44" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B147" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F147" t="s">
         <v>1647</v>
       </c>
     </row>
-    <row r="148" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A148" s="44" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B148" s="31" t="s">
+        <v>1824</v>
+      </c>
       <c r="F148" t="s">
         <v>1648</v>
       </c>
     </row>
-    <row r="149" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A149" s="44" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B149" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F149" t="s">
         <v>1649</v>
       </c>
     </row>
-    <row r="150" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A150" s="44" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B150" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F150" t="s">
         <v>1650</v>
       </c>
     </row>
-    <row r="151" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A151" s="44" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B151" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F151" t="s">
         <v>1651</v>
       </c>
     </row>
-    <row r="152" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A152" s="44" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B152" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F152" t="s">
         <v>1652</v>
       </c>
     </row>
-    <row r="153" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A153" s="44" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B153" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F153" t="s">
         <v>1653</v>
       </c>
     </row>
-    <row r="154" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A154" s="44" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B154" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F154" t="s">
         <v>1654</v>
       </c>
     </row>
-    <row r="155" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A155" s="44" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B155" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F155" t="s">
         <v>1655</v>
       </c>
     </row>
-    <row r="156" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A156" s="44" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B156" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F156" t="s">
         <v>1656</v>
       </c>
     </row>
-    <row r="157" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A157" s="44" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B157" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F157" t="s">
         <v>1657</v>
       </c>
     </row>
-    <row r="158" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A158" s="44" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B158" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F158" t="s">
         <v>1658</v>
       </c>
     </row>
-    <row r="159" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A159" s="44" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B159" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F159" t="s">
         <v>1659</v>
       </c>
     </row>
-    <row r="160" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A160" s="44" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B160" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F160" t="s">
         <v>1660</v>
       </c>
     </row>
-    <row r="161" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A161" s="44" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B161" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F161" t="s">
         <v>1334</v>
       </c>
     </row>
-    <row r="162" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A162" s="44" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B162" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F162" t="s">
         <v>1661</v>
       </c>
     </row>
-    <row r="163" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+      <c r="A163" s="44" t="s">
+        <v>1662</v>
+      </c>
       <c r="F163" t="s">
         <v>1662</v>
       </c>
     </row>
-    <row r="164" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+      <c r="A164" s="44">
+        <v>44</v>
+      </c>
       <c r="F164">
         <v>44</v>
       </c>
     </row>
-    <row r="165" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A165" s="44" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B165" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F165" t="s">
         <v>1663</v>
       </c>
     </row>
-    <row r="166" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A166" s="44" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B166" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F166" t="s">
         <v>1664</v>
       </c>
     </row>
-    <row r="167" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A167" s="44" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B167" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F167" t="s">
         <v>1665</v>
       </c>
     </row>
-    <row r="168" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A168" s="44" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B168" s="31" t="s">
+        <v>1829</v>
+      </c>
       <c r="F168" t="s">
         <v>1666</v>
       </c>
     </row>
-    <row r="169" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A169" s="44" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B169" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F169" t="s">
         <v>1667</v>
       </c>
     </row>
-    <row r="170" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A170" s="44" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B170" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F170" t="s">
         <v>1668</v>
       </c>
     </row>
-    <row r="171" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A171" s="44" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B171" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F171" t="s">
         <v>1669</v>
       </c>
     </row>
-    <row r="172" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A172" s="44" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B172" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F172" t="s">
         <v>1670</v>
       </c>
     </row>
-    <row r="173" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A173" s="44" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B173" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F173" t="s">
         <v>1671</v>
       </c>
     </row>
-    <row r="174" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A174" s="44" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B174" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F174" t="s">
         <v>1672</v>
       </c>
     </row>
-    <row r="175" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A175" s="44" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B175" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F175" t="s">
         <v>1673</v>
       </c>
     </row>
-    <row r="176" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A176" s="44" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B176" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F176" t="s">
         <v>1674</v>
       </c>
     </row>
-    <row r="177" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+      <c r="A177" s="44" t="s">
+        <v>1675</v>
+      </c>
       <c r="F177" t="s">
         <v>1675</v>
       </c>
     </row>
-    <row r="178" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A178" s="44" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B178" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F178" t="s">
         <v>1676</v>
       </c>
     </row>
-    <row r="179" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A179" s="44" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B179" s="33" t="s">
+        <v>1830</v>
+      </c>
       <c r="F179" t="s">
         <v>1677</v>
       </c>
     </row>
-    <row r="180" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A180" s="44" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B180" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F180" t="s">
         <v>1678</v>
       </c>
     </row>
-    <row r="181" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A181" s="44" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B181" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F181" t="s">
         <v>1679</v>
       </c>
     </row>
-    <row r="182" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A182" s="44" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B182" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F182" t="s">
         <v>1680</v>
       </c>
     </row>
-    <row r="183" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A183" s="44" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B183" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F183" t="s">
         <v>1681</v>
       </c>
     </row>
-    <row r="184" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A184" s="44" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B184" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F184" t="s">
         <v>1682</v>
       </c>
     </row>
-    <row r="185" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+      <c r="A185" s="44" t="s">
+        <v>1683</v>
+      </c>
       <c r="F185" t="s">
         <v>1683</v>
       </c>
     </row>
-    <row r="186" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A186" s="44" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B186" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F186" t="s">
         <v>1684</v>
       </c>
     </row>
-    <row r="187" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A187" s="44" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B187" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F187" t="s">
         <v>1685</v>
       </c>
     </row>
-    <row r="188" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A188" s="44" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B188" s="33" t="s">
+        <v>1834</v>
+      </c>
       <c r="F188" t="s">
         <v>1686</v>
       </c>
     </row>
-    <row r="189" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A189" s="44" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B189" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F189" t="s">
         <v>1687</v>
       </c>
     </row>
-    <row r="190" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A190" s="44" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B190" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F190" t="s">
         <v>1688</v>
       </c>
     </row>
-    <row r="191" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A191" s="44" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B191" s="31" t="s">
+        <v>1829</v>
+      </c>
       <c r="F191" t="s">
         <v>1689</v>
       </c>
     </row>
-    <row r="192" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A192" s="44" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B192" s="31" t="s">
+        <v>1829</v>
+      </c>
       <c r="F192" t="s">
         <v>1690</v>
       </c>
     </row>
-    <row r="193" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A193" s="44" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B193" s="31" t="s">
+        <v>1819</v>
+      </c>
       <c r="F193" t="s">
         <v>1691</v>
       </c>
     </row>
-    <row r="194" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A194" s="44" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B194" s="31" t="s">
+        <v>1827</v>
+      </c>
       <c r="F194" t="s">
         <v>1692</v>
       </c>
     </row>
-    <row r="195" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A195" s="44" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B195" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F195" t="s">
         <v>1693</v>
       </c>
     </row>
-    <row r="196" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A196" s="44" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B196" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F196" t="s">
         <v>1694</v>
       </c>
     </row>
-    <row r="197" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A197" s="44" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B197" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F197" t="s">
         <v>1695</v>
       </c>
     </row>
-    <row r="198" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A198" s="44" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B198" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F198" t="s">
         <v>1696</v>
       </c>
     </row>
-    <row r="199" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A199" s="44" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B199" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F199" t="s">
         <v>1697</v>
       </c>
     </row>
-    <row r="200" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A200" s="44" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B200" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F200" t="s">
         <v>1698</v>
       </c>
     </row>
-    <row r="201" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A201" s="44" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B201" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F201" t="s">
         <v>1699</v>
       </c>
     </row>
-    <row r="202" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A202" s="44" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B202" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F202" t="s">
         <v>1159</v>
       </c>
     </row>
-    <row r="203" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A203" s="44" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B203" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F203" t="s">
         <v>1700</v>
       </c>
     </row>
-    <row r="204" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A204" s="44" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B204" s="33" t="s">
+        <v>1830</v>
+      </c>
       <c r="F204" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="205" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A205" s="44" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B205" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F205" t="s">
         <v>1702</v>
       </c>
     </row>
-    <row r="206" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A206" s="44" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B206" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F206" t="s">
         <v>1703</v>
       </c>
     </row>
-    <row r="207" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A207" s="44" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B207" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F207" t="s">
         <v>1704</v>
       </c>
     </row>
-    <row r="208" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A208" s="44" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B208" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F208" t="s">
         <v>1705</v>
       </c>
     </row>
-    <row r="209" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A209" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F209" t="s">
         <v>1706</v>
       </c>
     </row>
-    <row r="210" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A210" s="44" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B210" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F210" t="s">
         <v>1707</v>
       </c>
     </row>
-    <row r="211" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A211" s="44" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B211" s="33" t="s">
+        <v>1834</v>
+      </c>
       <c r="F211" t="s">
         <v>1708</v>
       </c>
     </row>
-    <row r="212" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A212" s="44" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B212" s="33" t="s">
+        <v>1834</v>
+      </c>
       <c r="F212" t="s">
         <v>1709</v>
       </c>
     </row>
-    <row r="213" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A213" s="44" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B213" s="33" t="s">
+        <v>1834</v>
+      </c>
       <c r="F213" t="s">
         <v>1710</v>
       </c>
     </row>
-    <row r="214" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A214" s="44" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B214" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F214" t="s">
         <v>1711</v>
       </c>
     </row>
-    <row r="215" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A215" s="44" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B215" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F215" t="s">
         <v>1712</v>
       </c>
     </row>
-    <row r="216" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A216" s="44" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B216" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F216" t="s">
         <v>1713</v>
       </c>
     </row>
-    <row r="217" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A217" s="44" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B217" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F217" t="s">
         <v>1714</v>
       </c>
     </row>
-    <row r="218" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A218" s="44" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B218" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F218" t="s">
         <v>1715</v>
       </c>
     </row>
-    <row r="219" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A219" s="44" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B219" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F219" t="s">
         <v>1716</v>
       </c>
     </row>
-    <row r="220" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A220" s="44" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B220" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F220" t="s">
         <v>1717</v>
       </c>
     </row>
-    <row r="221" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A221" s="44" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B221" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F221" t="s">
         <v>1718</v>
       </c>
     </row>
-    <row r="222" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A222" s="44" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B222" s="31" t="s">
+        <v>1824</v>
+      </c>
       <c r="F222" t="s">
         <v>1719</v>
       </c>
     </row>
-    <row r="223" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A223" s="44" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B223" s="31" t="s">
+        <v>1824</v>
+      </c>
       <c r="F223" t="s">
         <v>1720</v>
       </c>
     </row>
-    <row r="224" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A224" s="44" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B224" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F224" t="s">
         <v>1721</v>
       </c>
     </row>
-    <row r="225" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A225" s="44" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B225" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F225" t="s">
         <v>1507</v>
       </c>
     </row>
-    <row r="226" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A226" s="44" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B226" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F226" t="s">
         <v>1722</v>
       </c>
     </row>
-    <row r="227" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A227" s="44" t="s">
+        <v>1723</v>
+      </c>
       <c r="F227" t="s">
         <v>1723</v>
       </c>
     </row>
-    <row r="228" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A228" s="44" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B228" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F228" t="s">
         <v>1724</v>
       </c>
     </row>
-    <row r="229" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+      <c r="A229" s="44">
+        <v>15800000</v>
+      </c>
       <c r="F229">
         <v>15800000</v>
       </c>
     </row>
-    <row r="230" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+      <c r="A230" s="44">
+        <v>5000000</v>
+      </c>
       <c r="F230">
         <v>5000000</v>
       </c>
     </row>
-    <row r="231" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+      <c r="A231" s="44">
+        <v>8160000</v>
+      </c>
       <c r="F231">
         <v>8160000</v>
       </c>
     </row>
-    <row r="232" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A232" s="44" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B232" s="33" t="s">
+        <v>1830</v>
+      </c>
       <c r="F232" t="s">
         <v>1725</v>
       </c>
     </row>
-    <row r="233" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A233" s="44" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B233" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F233" t="s">
         <v>1726</v>
       </c>
     </row>
-    <row r="234" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+      <c r="A234" s="44" t="s">
+        <v>1727</v>
+      </c>
       <c r="F234" t="s">
         <v>1727</v>
       </c>
     </row>
-    <row r="235" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A235" s="44" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B235" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F235" t="s">
         <v>1728</v>
       </c>
     </row>
-    <row r="236" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A236" s="44" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B236" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F236" t="s">
         <v>1729</v>
       </c>
     </row>
-    <row r="237" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A237" s="44" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B237" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F237" t="s">
         <v>1730</v>
       </c>
     </row>
-    <row r="238" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A238" s="44" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B238" s="33" t="s">
+        <v>1830</v>
+      </c>
       <c r="F238" t="s">
         <v>1731</v>
       </c>
     </row>
-    <row r="239" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A239" s="44" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B239" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F239" t="s">
         <v>1732</v>
       </c>
     </row>
-    <row r="240" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A240" s="44" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B240" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F240" t="s">
         <v>1733</v>
       </c>
     </row>
-    <row r="241" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A241" s="44" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B241" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F241" t="s">
         <v>1734</v>
       </c>
     </row>
-    <row r="242" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A242" s="44" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B242" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F242" t="s">
         <v>1735</v>
       </c>
     </row>
-    <row r="243" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A243" s="44" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B243" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F243" t="s">
         <v>1736</v>
       </c>
     </row>
-    <row r="244" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A244" s="44" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B244" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F244" t="s">
         <v>1737</v>
       </c>
     </row>
-    <row r="245" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A245" s="44" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B245" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F245" t="s">
         <v>1738</v>
       </c>
     </row>
-    <row r="246" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A246" s="44" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B246" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F246" t="s">
         <v>1739</v>
       </c>
     </row>
-    <row r="247" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A247" s="44" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B247" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F247" t="s">
         <v>1740</v>
       </c>
     </row>
-    <row r="248" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A248" s="44" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B248" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F248" t="s">
         <v>1741</v>
       </c>
     </row>
-    <row r="249" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A249" s="44" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B249" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F249" t="s">
         <v>1742</v>
       </c>
     </row>
-    <row r="250" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
       <c r="F250" t="s">
         <v>1743</v>
       </c>
     </row>
-    <row r="251" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A251" s="44" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B251" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F251" t="s">
         <v>1744</v>
       </c>
     </row>
-    <row r="252" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A252" s="44" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B252" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F252" t="s">
         <v>1745</v>
       </c>
     </row>
-    <row r="253" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A253" s="44" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B253" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F253" t="s">
         <v>1746</v>
       </c>
     </row>
-    <row r="254" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A254" s="44" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B254" s="31" t="s">
+        <v>1829</v>
+      </c>
       <c r="F254" t="s">
         <v>1747</v>
       </c>
     </row>
-    <row r="255" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A255" s="44" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B255" s="31" t="s">
+        <v>1827</v>
+      </c>
       <c r="F255" t="s">
         <v>1748</v>
       </c>
     </row>
-    <row r="256" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A256" s="44" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B256" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F256" t="s">
         <v>1749</v>
       </c>
     </row>
-    <row r="257" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A257" s="44" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B257" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F257" t="s">
         <v>1750</v>
       </c>
     </row>
-    <row r="258" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A258" s="44" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B258" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F258" t="s">
         <v>1751</v>
       </c>
     </row>
-    <row r="259" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A259" s="44" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B259" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F259" t="s">
         <v>1752</v>
       </c>
     </row>
-    <row r="260" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A260" s="44" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B260" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F260" t="s">
         <v>1753</v>
       </c>
     </row>
-    <row r="261" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A261" s="44" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B261" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F261" t="s">
         <v>1754</v>
       </c>
     </row>
-    <row r="262" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A262" s="44" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B262" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F262" t="s">
         <v>1755</v>
       </c>
     </row>
-    <row r="263" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A263" s="44" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B263" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F263" t="s">
         <v>1756</v>
       </c>
     </row>
-    <row r="264" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A264" s="44" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B264" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F264" t="s">
         <v>1757</v>
       </c>
     </row>
-    <row r="265" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A265" s="44" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B265" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F265" t="s">
         <v>1758</v>
       </c>
     </row>
-    <row r="266" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A266" s="44" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B266" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F266" t="s">
         <v>1759</v>
       </c>
     </row>
-    <row r="267" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A267" s="44" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B267" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F267" t="s">
         <v>1760</v>
       </c>
     </row>
-    <row r="268" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A268" s="44" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B268" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F268" t="s">
         <v>1761</v>
       </c>
     </row>
-    <row r="269" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A269" s="44" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B269" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F269" t="s">
         <v>1762</v>
       </c>
     </row>
-    <row r="270" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A270" s="44" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B270" s="33" t="s">
+        <v>1833</v>
+      </c>
       <c r="F270" t="s">
         <v>1763</v>
       </c>
     </row>
-    <row r="271" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A271" s="44" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B271" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F271" t="s">
         <v>1764</v>
       </c>
     </row>
-    <row r="272" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A272" s="44" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B272" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F272" t="s">
         <v>1765</v>
       </c>
     </row>
-    <row r="273" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A273" s="44" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B273" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F273" t="s">
         <v>1766</v>
       </c>
     </row>
-    <row r="274" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A274" s="44" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B274" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F274" t="s">
         <v>1767</v>
       </c>
     </row>
-    <row r="275" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A275" s="44" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B275" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F275" t="s">
         <v>1768</v>
       </c>
     </row>
-    <row r="276" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A276" s="44" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B276" s="33" t="s">
+        <v>1833</v>
+      </c>
       <c r="F276" t="s">
         <v>1769</v>
       </c>
     </row>
-    <row r="277" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A277" s="44" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B277" s="34" t="s">
+        <v>1837</v>
+      </c>
       <c r="F277" t="s">
         <v>1770</v>
       </c>
     </row>
-    <row r="278" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A278" s="44" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B278" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F278" t="s">
         <v>1771</v>
       </c>
     </row>
-    <row r="279" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:6" ht="32" x14ac:dyDescent="0.35">
+      <c r="A279" s="44" t="s">
+        <v>1772</v>
+      </c>
       <c r="F279" t="s">
         <v>1772</v>
       </c>
     </row>
-    <row r="280" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A280" s="44" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B280" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F280" t="s">
         <v>1773</v>
       </c>
     </row>
-    <row r="281" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A281" s="44" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B281" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F281" t="s">
         <v>1774</v>
       </c>
     </row>
-    <row r="282" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A282" s="44" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B282" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F282" t="s">
         <v>1775</v>
       </c>
     </row>
-    <row r="283" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A283" s="44" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B283" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F283" t="s">
         <v>1776</v>
       </c>
     </row>
-    <row r="284" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A284" s="44" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B284" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F284" t="s">
         <v>1777</v>
       </c>
     </row>
-    <row r="285" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A285" s="44" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B285" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F285" t="s">
         <v>1778</v>
       </c>
     </row>
-    <row r="286" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A286" s="44" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B286" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F286" t="s">
         <v>1779</v>
       </c>
     </row>
-    <row r="287" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A287" s="44" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B287" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F287" t="s">
         <v>1780</v>
       </c>
     </row>
-    <row r="288" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:6" ht="16" x14ac:dyDescent="0.35">
+      <c r="A288" s="44">
+        <v>74</v>
+      </c>
       <c r="F288">
         <v>74</v>
       </c>
     </row>
-    <row r="289" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A289" s="44" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B289" s="33" t="s">
+        <v>1830</v>
+      </c>
       <c r="F289" t="s">
         <v>1781</v>
       </c>
     </row>
-    <row r="290" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A290" s="44" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B290" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F290" t="s">
         <v>1782</v>
       </c>
     </row>
-    <row r="291" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A291" s="44" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B291" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F291" t="s">
         <v>1783</v>
       </c>
     </row>
-    <row r="292" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A292" s="44" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B292" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F292" t="s">
         <v>1784</v>
       </c>
     </row>
-    <row r="293" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A293" s="44" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B293" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F293" t="s">
         <v>1785</v>
       </c>
     </row>
-    <row r="294" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A294" s="44" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B294" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F294" t="s">
         <v>1786</v>
       </c>
     </row>
-    <row r="295" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A295" s="44" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B295" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F295" t="s">
         <v>1787</v>
       </c>
     </row>
-    <row r="296" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A296" s="44" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B296" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F296" t="s">
         <v>1788</v>
       </c>
     </row>
-    <row r="297" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A297" s="44" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B297" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F297" t="s">
         <v>1789</v>
       </c>
     </row>
-    <row r="298" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A298" s="44" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B298" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F298" t="s">
         <v>1790</v>
       </c>
     </row>
-    <row r="299" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A299" s="44" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B299" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F299" t="s">
         <v>1791</v>
       </c>
     </row>
-    <row r="300" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A300" s="44" t="s">
+        <v>1792</v>
+      </c>
+      <c r="B300" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F300" t="s">
         <v>1792</v>
       </c>
     </row>
-    <row r="301" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A301" s="44" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B301" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F301" t="s">
         <v>1793</v>
       </c>
     </row>
-    <row r="302" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A302" s="44" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B302" s="31" t="s">
+        <v>1829</v>
+      </c>
       <c r="F302" t="s">
         <v>1794</v>
       </c>
     </row>
-    <row r="303" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A303" s="44" t="s">
+        <v>1795</v>
+      </c>
+      <c r="B303" s="31" t="s">
+        <v>1829</v>
+      </c>
       <c r="F303" t="s">
         <v>1795</v>
       </c>
     </row>
-    <row r="304" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A304" s="44" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B304" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F304" t="s">
         <v>1796</v>
       </c>
     </row>
-    <row r="305" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A305" s="44" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B305" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F305" t="s">
         <v>1797</v>
       </c>
     </row>
-    <row r="306" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A306" s="44" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B306" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F306" t="s">
         <v>1798</v>
       </c>
     </row>
-    <row r="307" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A307" s="44" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B307" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F307" t="s">
         <v>1799</v>
       </c>
     </row>
-    <row r="308" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A308" s="44" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B308" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F308" t="s">
         <v>1800</v>
       </c>
     </row>
-    <row r="309" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A309" s="44" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B309" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F309" t="s">
         <v>1801</v>
       </c>
     </row>
-    <row r="310" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A310" s="44" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B310" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F310" t="s">
         <v>1802</v>
       </c>
     </row>
-    <row r="311" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A311" s="44" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B311" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F311" t="s">
         <v>1803</v>
       </c>
     </row>
-    <row r="312" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A312" s="44" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B312" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F312" t="s">
         <v>1804</v>
       </c>
     </row>
-    <row r="313" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A313" s="44" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B313" s="31" t="s">
+        <v>1829</v>
+      </c>
       <c r="F313" t="s">
         <v>1805</v>
       </c>
     </row>
-    <row r="314" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A314" s="44" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B314" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F314" t="s">
         <v>1806</v>
       </c>
     </row>
-    <row r="315" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A315" s="44" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B315" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F315" t="s">
         <v>1807</v>
       </c>
     </row>
-    <row r="316" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A316" s="44" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B316" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F316" t="s">
         <v>1808</v>
       </c>
     </row>
-    <row r="317" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A317" s="44" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B317" s="31" t="s">
+        <v>1823</v>
+      </c>
       <c r="F317" t="s">
         <v>1809</v>
       </c>
     </row>
-    <row r="318" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A318" s="44" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B318" s="33" t="s">
+        <v>1830</v>
+      </c>
       <c r="F318" t="s">
         <v>1810</v>
       </c>
     </row>
-    <row r="319" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A319" s="44" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B319" s="33" t="s">
+        <v>1834</v>
+      </c>
       <c r="F319" t="s">
         <v>1811</v>
       </c>
     </row>
-    <row r="320" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:6" ht="32.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A320" s="44" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B320" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F320" t="s">
         <v>1812</v>
       </c>
     </row>
-    <row r="321" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A321" s="44" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B321" s="31" t="s">
+        <v>1826</v>
+      </c>
       <c r="F321" t="s">
         <v>1813</v>
       </c>
     </row>
-    <row r="322" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A322" s="44" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B322" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F322" t="s">
         <v>1814</v>
       </c>
     </row>
-    <row r="323" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A323" s="44" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B323" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F323" t="s">
         <v>1815</v>
       </c>
     </row>
-    <row r="324" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A324" s="44" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B324" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F324" t="s">
         <v>1816</v>
       </c>
     </row>
-    <row r="325" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A325" s="44" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B325" s="31" t="s">
+        <v>1694</v>
+      </c>
       <c r="F325" t="s">
         <v>1817</v>
       </c>
     </row>
-    <row r="326" spans="6:6" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A326" s="44" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B326" s="29" t="s">
+        <v>1821</v>
+      </c>
       <c r="F326" t="s">
         <v>1818</v>
       </c>
